--- a/diseases/d144/2010-2014.xlsx
+++ b/diseases/d144/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2841,9 +2832,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3533,9 +3521,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -4225,9 +4210,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4917,9 +4899,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5609,9 +5588,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6301,9 +6277,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6993,9 +6966,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -7685,9 +7655,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -8377,9 +8344,6 @@
       <c r="O46" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -9069,9 +9033,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9909,9 +9870,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10305,9 +10263,6 @@
       <c r="O57" t="n">
         <v>4</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -10453,9 +10408,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -11293,9 +11245,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11441,9 +11390,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -12281,9 +12227,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12429,9 +12372,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13269,9 +13209,6 @@
       <c r="O75" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -13417,9 +13354,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14257,9 +14191,6 @@
       <c r="O81" t="n">
         <v>3</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -14405,9 +14336,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -15245,9 +15173,6 @@
       <c r="O87" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -15393,9 +15318,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16233,9 +16155,6 @@
       <c r="O93" t="n">
         <v>5</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01017756937598686</v>
       </c>
@@ -16381,9 +16300,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -17221,9 +17137,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -17369,9 +17282,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18209,9 +18119,6 @@
       <c r="O105" t="n">
         <v>4</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -18357,9 +18264,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19197,9 +19101,6 @@
       <c r="O111" t="n">
         <v>5</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.01017756937598686</v>
       </c>
@@ -19345,9 +19246,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20185,9 +20083,6 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -20333,9 +20228,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -21173,9 +21065,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -21321,9 +21210,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -22161,9 +22047,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22557,9 +22440,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22705,9 +22585,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23545,9 +23422,6 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.00604843837436162</v>
       </c>
@@ -23693,9 +23567,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -24533,9 +24404,6 @@
       <c r="O143" t="n">
         <v>2</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -24681,9 +24549,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -25521,9 +25386,6 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -25669,9 +25531,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -26509,9 +26368,6 @@
       <c r="O155" t="n">
         <v>4</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.008064584499148828</v>
       </c>
@@ -26657,9 +26513,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -27497,9 +27350,6 @@
       <c r="O161" t="n">
         <v>9</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.01814531512308486</v>
       </c>
@@ -27645,9 +27495,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -28485,9 +28332,6 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.008064584499148828</v>
       </c>
@@ -28633,9 +28477,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -29473,9 +29314,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -29621,9 +29459,6 @@
       <c r="O174" t="n">
         <v>2</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -30461,9 +30296,6 @@
       <c r="O179" t="n">
         <v>4</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.008064584499148828</v>
       </c>
@@ -30609,9 +30441,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -31893,9 +31722,6 @@
       <c r="O188" t="n">
         <v>4</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.008064584499148828</v>
       </c>
@@ -32041,9 +31867,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33473,9 +33296,6 @@
       <c r="O198" t="n">
         <v>7</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.01411302287351045</v>
       </c>
@@ -33621,9 +33441,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -35201,9 +35018,6 @@
       <c r="O209" t="n">
         <v>5</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.01008073062393603</v>
       </c>
@@ -35349,9 +35163,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -36929,9 +36740,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -37325,9 +37133,6 @@
       <c r="O222" t="n">
         <v>4</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -37473,9 +37278,6 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -39053,9 +38855,6 @@
       <c r="O233" t="n">
         <v>4</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -39201,9 +39000,6 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -40633,9 +40429,6 @@
       <c r="O243" t="n">
         <v>2</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -40781,9 +40574,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -42213,9 +42003,6 @@
       <c r="O253" t="n">
         <v>4</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -42361,9 +42148,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -43793,9 +43577,6 @@
       <c r="O263" t="n">
         <v>3</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -43941,9 +43722,6 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -45521,9 +45299,6 @@
       <c r="O274" t="n">
         <v>5</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.009985787328752859</v>
       </c>
@@ -45669,9 +45444,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -47101,9 +46873,6 @@
       <c r="O284" t="n">
         <v>2</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -47249,9 +47018,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -48681,9 +48447,6 @@
       <c r="O294" t="n">
         <v>3</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -48829,9 +48592,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -50409,9 +50169,6 @@
       <c r="O305" t="n">
         <v>3</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -50557,9 +50314,6 @@
       <c r="O306" t="n">
         <v>2</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.03936911388687422</v>
       </c>
@@ -51989,9 +51743,6 @@
       <c r="O315" t="n">
         <v>3</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -52137,9 +51888,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -53717,9 +53465,6 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -53865,9 +53610,6 @@
       <c r="O327" t="n">
         <v>1</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -55297,9 +55039,6 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
@@ -55445,9 +55184,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -57025,9 +56761,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -57421,9 +57154,6 @@
       <c r="O349" t="n">
         <v>4</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -57569,9 +57299,6 @@
       <c r="O350" t="n">
         <v>2</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -59149,9 +58876,6 @@
       <c r="O360" t="n">
         <v>4</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -59297,9 +59021,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -60729,9 +60450,6 @@
       <c r="O370" t="n">
         <v>4</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -60877,9 +60595,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -62309,9 +62024,6 @@
       <c r="O380" t="n">
         <v>3</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -62457,9 +62169,6 @@
       <c r="O381" t="n">
         <v>1</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -63889,9 +63598,6 @@
       <c r="O390" t="n">
         <v>4</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -64037,9 +63743,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -65617,9 +65320,6 @@
       <c r="O401" t="n">
         <v>2</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -65765,9 +65465,6 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
@@ -67197,9 +66894,6 @@
       <c r="O411" t="n">
         <v>8</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.01582934212136197</v>
       </c>
@@ -67345,9 +67039,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -68925,9 +68616,6 @@
       <c r="O422" t="n">
         <v>0</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0</v>
       </c>
@@ -69073,9 +68761,6 @@
       <c r="O423" t="n">
         <v>1</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -70505,9 +70190,6 @@
       <c r="O432" t="n">
         <v>6</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.01187200659102147</v>
       </c>
@@ -70653,9 +70335,6 @@
       <c r="O433" t="n">
         <v>1</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -72085,9 +71764,6 @@
       <c r="O442" t="n">
         <v>7</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0.01385067435619172</v>
       </c>
@@ -72233,9 +71909,6 @@
       <c r="O443" t="n">
         <v>1</v>
       </c>
-      <c r="Q443" t="n">
-        <v>0</v>
-      </c>
       <c r="R443" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -73813,9 +73486,6 @@
       <c r="O453" t="n">
         <v>9</v>
       </c>
-      <c r="Q453" t="n">
-        <v>0</v>
-      </c>
       <c r="R453" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -73961,9 +73631,6 @@
       <c r="O454" t="n">
         <v>0</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0</v>
       </c>
@@ -75393,9 +75060,6 @@
       <c r="O463" t="n">
         <v>14</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0.02770134871238344</v>
       </c>
@@ -75539,9 +75203,6 @@
         <v>0</v>
       </c>
       <c r="O464" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q464" t="n">
         <v>0</v>
       </c>
       <c r="R464" t="n">
